--- a/branches/migration/2026.0.4-template-v0.13.0/StructureDefinition-mii-pr-molgen-therapeutische-implikation.xlsx
+++ b/branches/migration/2026.0.4-template-v0.13.0/StructureDefinition-mii-pr-molgen-therapeutische-implikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:16:36+00:00</t>
+    <t>2026-08-28T15:28:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.4-template-v0.13.0/StructureDefinition-mii-pr-molgen-therapeutische-implikation.xlsx
+++ b/branches/migration/2026.0.4-template-v0.13.0/StructureDefinition-mii-pr-molgen-therapeutische-implikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:28:23+00:00</t>
+    <t>2026-08-28T15:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.4-template-v0.13.0/StructureDefinition-mii-pr-molgen-therapeutische-implikation.xlsx
+++ b/branches/migration/2026.0.4-template-v0.13.0/StructureDefinition-mii-pr-molgen-therapeutische-implikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:36:04+00:00</t>
+    <t>2026-08-28T15:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
